--- a/Cochin-April-2025.xlsx
+++ b/Cochin-April-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Cochin</t>
   </si>
   <si>
@@ -115,13 +118,13 @@
     <t>KL07DF3416</t>
   </si>
   <si>
-    <t>Dzire</t>
-  </si>
-  <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Citroen</t>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>URBANIA</t>
@@ -131,6 +134,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -183,11 +189,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,10 +489,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -564,27 +571,30 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>230</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2">
         <v>45087</v>
       </c>
       <c r="H2">
@@ -645,26 +655,26 @@
         <v>9.81</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>231</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3">
+        <v>35</v>
+      </c>
+      <c r="G3" s="2">
         <v>43641</v>
       </c>
       <c r="H3">
@@ -725,26 +735,26 @@
         <v>54.23</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>232</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4">
+        <v>35</v>
+      </c>
+      <c r="G4" s="2">
         <v>44460</v>
       </c>
       <c r="H4">
@@ -805,26 +815,26 @@
         <v>49.07</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>233</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5">
+        <v>36</v>
+      </c>
+      <c r="G5" s="2">
         <v>45489</v>
       </c>
       <c r="H5">
@@ -885,26 +895,26 @@
         <v>74.03</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6">
+        <v>37</v>
+      </c>
+      <c r="G6" s="2">
         <v>45680</v>
       </c>
       <c r="H6">
